--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260502_203249.xlsx
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
